--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\GDOforecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79A500C-CDF6-49F3-BCBC-4AF966E01D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAB4475-7967-444E-9FC9-40C952D7DD2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32070" yWindow="3060" windowWidth="24675" windowHeight="12765" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33870" yWindow="2655" windowWidth="19380" windowHeight="12135" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
@@ -8515,6 +8515,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63ED8BDC-A713-430C-AA0F-98328B9D02BC}">
   <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
